--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -30226,6 +30226,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1299">
+      <c r="A1299" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1299" t="n">
+        <v>22500</v>
+      </c>
+      <c r="C1299" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="D1299" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="E1299" t="n">
+        <v>0.400999993085861</v>
+      </c>
+      <c r="F1299" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G1299" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -30249,6 +30249,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1300">
+      <c r="A1300" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1300" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1300" t="n">
+        <v>0.395999997854233</v>
+      </c>
+      <c r="D1300" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="E1300" t="n">
+        <v>0.391000002622604</v>
+      </c>
+      <c r="F1300" t="n">
+        <v>0.395999997854233</v>
+      </c>
+      <c r="G1300" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -30272,6 +30272,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1301">
+      <c r="A1301" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1301" t="n">
+        <v>13500</v>
+      </c>
+      <c r="C1301" t="n">
+        <v>0.393999993801117</v>
+      </c>
+      <c r="D1301" t="n">
+        <v>0.382999986410141</v>
+      </c>
+      <c r="E1301" t="n">
+        <v>0.382999986410141</v>
+      </c>
+      <c r="F1301" t="n">
+        <v>0.395000010728836</v>
+      </c>
+      <c r="G1301" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -30280,7 +30280,7 @@
         <v>13500</v>
       </c>
       <c r="C1301" t="n">
-        <v>0.393999993801117</v>
+        <v>0.395000010728836</v>
       </c>
       <c r="D1301" t="n">
         <v>0.382999986410141</v>
@@ -30292,6 +30292,29 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G1301" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1302" t="n">
+        <v>10500</v>
+      </c>
+      <c r="C1302" t="n">
+        <v>0.397000014781952</v>
+      </c>
+      <c r="D1302" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="E1302" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="F1302" t="n">
+        <v>0.397000014781952</v>
+      </c>
+      <c r="G1302" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -30136,22 +30136,22 @@
     </row>
     <row r="1295">
       <c r="A1295" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1295" t="n">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="C1295" t="n">
-        <v>0.418999999761581</v>
+        <v>0.419999986886978</v>
       </c>
       <c r="D1295" t="n">
-        <v>0.400999993085861</v>
+        <v>0.419999986886978</v>
       </c>
       <c r="E1295" t="n">
-        <v>0.418999999761581</v>
+        <v>0.419999986886978</v>
       </c>
       <c r="F1295" t="n">
-        <v>0.400999993085861</v>
+        <v>0.419999986886978</v>
       </c>
       <c r="G1295" t="s">
         <v>7</v>
@@ -30159,22 +30159,22 @@
     </row>
     <row r="1296">
       <c r="A1296" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1296" t="n">
-        <v>30000</v>
+        <v>36000</v>
       </c>
       <c r="C1296" t="n">
+        <v>0.418999999761581</v>
+      </c>
+      <c r="D1296" t="n">
         <v>0.400999993085861</v>
       </c>
-      <c r="D1296" t="n">
-        <v>0.388000011444092</v>
-      </c>
       <c r="E1296" t="n">
+        <v>0.418999999761581</v>
+      </c>
+      <c r="F1296" t="n">
         <v>0.400999993085861</v>
-      </c>
-      <c r="F1296" t="n">
-        <v>0.388999998569489</v>
       </c>
       <c r="G1296" t="s">
         <v>7</v>
@@ -30182,22 +30182,22 @@
     </row>
     <row r="1297">
       <c r="A1297" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1297" t="n">
-        <v>52500</v>
+        <v>30000</v>
       </c>
       <c r="C1297" t="n">
-        <v>0.40200001001358</v>
+        <v>0.400999993085861</v>
       </c>
       <c r="D1297" t="n">
-        <v>0.384999990463257</v>
+        <v>0.388000011444092</v>
       </c>
       <c r="E1297" t="n">
-        <v>0.398999989032745</v>
+        <v>0.400999993085861</v>
       </c>
       <c r="F1297" t="n">
-        <v>0.393999993801117</v>
+        <v>0.388999998569489</v>
       </c>
       <c r="G1297" t="s">
         <v>7</v>
@@ -30205,22 +30205,22 @@
     </row>
     <row r="1298">
       <c r="A1298" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1298" t="n">
-        <v>6000</v>
+        <v>52500</v>
       </c>
       <c r="C1298" t="n">
-        <v>0.400999993085861</v>
+        <v>0.40200001001358</v>
       </c>
       <c r="D1298" t="n">
-        <v>0.386000007390976</v>
+        <v>0.384999990463257</v>
       </c>
       <c r="E1298" t="n">
-        <v>0.386000007390976</v>
+        <v>0.398999989032745</v>
       </c>
       <c r="F1298" t="n">
-        <v>0.400999993085861</v>
+        <v>0.393999993801117</v>
       </c>
       <c r="G1298" t="s">
         <v>7</v>
@@ -30228,22 +30228,22 @@
     </row>
     <row r="1299">
       <c r="A1299" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1299" t="n">
-        <v>22500</v>
+        <v>6000</v>
       </c>
       <c r="C1299" t="n">
-        <v>0.419999986886978</v>
+        <v>0.400999993085861</v>
       </c>
       <c r="D1299" t="n">
-        <v>0.400000005960464</v>
+        <v>0.386000007390976</v>
       </c>
       <c r="E1299" t="n">
+        <v>0.386000007390976</v>
+      </c>
+      <c r="F1299" t="n">
         <v>0.400999993085861</v>
-      </c>
-      <c r="F1299" t="n">
-        <v>0.400000005960464</v>
       </c>
       <c r="G1299" t="s">
         <v>7</v>
@@ -30251,22 +30251,22 @@
     </row>
     <row r="1300">
       <c r="A1300" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1300" t="n">
-        <v>9000</v>
+        <v>22500</v>
       </c>
       <c r="C1300" t="n">
-        <v>0.395999997854233</v>
+        <v>0.419999986886978</v>
       </c>
       <c r="D1300" t="n">
-        <v>0.389999985694885</v>
+        <v>0.400000005960464</v>
       </c>
       <c r="E1300" t="n">
-        <v>0.391000002622604</v>
+        <v>0.400999993085861</v>
       </c>
       <c r="F1300" t="n">
-        <v>0.395999997854233</v>
+        <v>0.400000005960464</v>
       </c>
       <c r="G1300" t="s">
         <v>7</v>
@@ -30274,22 +30274,22 @@
     </row>
     <row r="1301">
       <c r="A1301" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1301" t="n">
-        <v>13500</v>
+        <v>9000</v>
       </c>
       <c r="C1301" t="n">
-        <v>0.395000010728836</v>
+        <v>0.395999997854233</v>
       </c>
       <c r="D1301" t="n">
-        <v>0.382999986410141</v>
+        <v>0.389999985694885</v>
       </c>
       <c r="E1301" t="n">
-        <v>0.382999986410141</v>
+        <v>0.391000002622604</v>
       </c>
       <c r="F1301" t="n">
-        <v>0.395000010728836</v>
+        <v>0.395999997854233</v>
       </c>
       <c r="G1301" t="s">
         <v>7</v>
@@ -30297,24 +30297,47 @@
     </row>
     <row r="1302">
       <c r="A1302" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1302" t="n">
-        <v>10500</v>
+        <v>13500</v>
       </c>
       <c r="C1302" t="n">
-        <v>0.397000014781952</v>
+        <v>0.395000010728836</v>
       </c>
       <c r="D1302" t="n">
+        <v>0.382999986410141</v>
+      </c>
+      <c r="E1302" t="n">
+        <v>0.382999986410141</v>
+      </c>
+      <c r="F1302" t="n">
+        <v>0.395000010728836</v>
+      </c>
+      <c r="G1302" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1303" t="n">
+        <v>79500</v>
+      </c>
+      <c r="C1303" t="n">
+        <v>0.407000005245209</v>
+      </c>
+      <c r="D1303" t="n">
         <v>0.389999985694885</v>
       </c>
-      <c r="E1302" t="n">
-        <v>0.389999985694885</v>
-      </c>
-      <c r="F1302" t="n">
-        <v>0.397000014781952</v>
-      </c>
-      <c r="G1302" t="s">
+      <c r="E1303" t="n">
+        <v>0.391000002622604</v>
+      </c>
+      <c r="F1303" t="n">
+        <v>0.407000005245209</v>
+      </c>
+      <c r="G1303" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -30387,6 +30387,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1306">
+      <c r="A1306" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1306" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1306" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="D1306" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="E1306" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F1306" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G1306" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -34383,6 +34383,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1309">
+      <c r="A1309" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1309" t="n">
+        <v>463500</v>
+      </c>
+      <c r="C1309" t="n">
+        <v>0.497000008821487</v>
+      </c>
+      <c r="D1309" t="n">
+        <v>0.39300000667572</v>
+      </c>
+      <c r="E1309" t="n">
+        <v>0.407000005245209</v>
+      </c>
+      <c r="F1309" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="G1309" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="H1309" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -34461,6 +34461,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1312">
+      <c r="A1312" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1312" t="n">
+        <v>201000</v>
+      </c>
+      <c r="C1312" t="n">
+        <v>0.46000000834465</v>
+      </c>
+      <c r="D1312" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="E1312" t="n">
+        <v>0.453000009059906</v>
+      </c>
+      <c r="F1312" t="n">
+        <v>0.456999987363815</v>
+      </c>
+      <c r="G1312" t="n">
+        <v>0.456999987363815</v>
+      </c>
+      <c r="H1312" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -30610,8 +30610,31 @@
       <c r="E1315" t="n">
         <v>0.439999997615814</v>
       </c>
-      <c r="F1315"/>
+      <c r="F1315" t="n">
+        <v>0.453999996185303</v>
+      </c>
       <c r="G1315" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1316" t="n">
+        <v>36000</v>
+      </c>
+      <c r="C1316" t="n">
+        <v>0.46900001168251</v>
+      </c>
+      <c r="D1316" t="n">
+        <v>0.453000009059906</v>
+      </c>
+      <c r="E1316" t="n">
+        <v>0.465000003576279</v>
+      </c>
+      <c r="F1316"/>
+      <c r="G1316" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -30628,13 +30628,36 @@
         <v>0.46900001168251</v>
       </c>
       <c r="D1316" t="n">
-        <v>0.453000009059906</v>
+        <v>0.455000013113022</v>
       </c>
       <c r="E1316" t="n">
         <v>0.465000003576279</v>
       </c>
-      <c r="F1316"/>
+      <c r="F1316" t="n">
+        <v>0.46000000834465</v>
+      </c>
       <c r="G1316" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1317" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C1317" t="n">
+        <v>0.46000000834465</v>
+      </c>
+      <c r="D1317" t="n">
+        <v>0.449999988079071</v>
+      </c>
+      <c r="E1317" t="n">
+        <v>0.46000000834465</v>
+      </c>
+      <c r="F1317"/>
+      <c r="G1317" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -30656,8 +30656,31 @@
       <c r="E1317" t="n">
         <v>0.46000000834465</v>
       </c>
-      <c r="F1317"/>
+      <c r="F1317" t="n">
+        <v>0.449999988079071</v>
+      </c>
       <c r="G1317" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1318" t="n">
+        <v>55500</v>
+      </c>
+      <c r="C1318" t="n">
+        <v>0.485000014305115</v>
+      </c>
+      <c r="D1318" t="n">
+        <v>0.458000004291534</v>
+      </c>
+      <c r="E1318" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="F1318"/>
+      <c r="G1318" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -30679,8 +30679,31 @@
       <c r="E1318" t="n">
         <v>0.462000012397766</v>
       </c>
-      <c r="F1318"/>
+      <c r="F1318" t="n">
+        <v>0.485000014305115</v>
+      </c>
       <c r="G1318" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1319" t="n">
+        <v>19500</v>
+      </c>
+      <c r="C1319" t="n">
+        <v>0.485000014305115</v>
+      </c>
+      <c r="D1319" t="n">
+        <v>0.472000002861023</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>0.47299998998642</v>
+      </c>
+      <c r="F1319"/>
+      <c r="G1319" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -30709,6 +30709,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1320">
+      <c r="A1320" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1320" t="n">
+        <v>49500</v>
+      </c>
+      <c r="C1320" t="n">
+        <v>0.497999995946884</v>
+      </c>
+      <c r="D1320" t="n">
+        <v>0.476000010967255</v>
+      </c>
+      <c r="E1320" t="n">
+        <v>0.485000014305115</v>
+      </c>
+      <c r="F1320" t="n">
+        <v>0.49099999666214</v>
+      </c>
+      <c r="G1320" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -30778,6 +30778,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1323">
+      <c r="A1323" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1323" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1323" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="D1323" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="E1323" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="F1323" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="G1323" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -38774,6 +38774,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1325">
+      <c r="A1325" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1325" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1325" t="n">
+        <v>0.495000004768372</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>0.495000004768372</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>0.474000006914139</v>
+      </c>
+      <c r="F1325" t="n">
+        <v>0.474000006914139</v>
+      </c>
+      <c r="G1325" t="n">
+        <v>0.474000006914139</v>
+      </c>
+      <c r="H1325" t="n">
+        <v>27000</v>
+      </c>
+      <c r="I1325" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1326" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1326" t="n">
+        <v>0.474999994039536</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>0.474999994039536</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>0.474999994039536</v>
+      </c>
+      <c r="F1326" t="n">
+        <v>0.474999994039536</v>
+      </c>
+      <c r="G1326" t="n">
+        <v>0.474999994039536</v>
+      </c>
+      <c r="H1326" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I1326" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -38832,6 +38832,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1327">
+      <c r="A1327" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1327" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1327" t="n">
+        <v>0.476000010967255</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>0.476000010967255</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>0.476000010967255</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>0.476000010967255</v>
+      </c>
+      <c r="G1327" t="n">
+        <v>0.476000010967255</v>
+      </c>
+      <c r="H1327" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I1327" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -38861,6 +38861,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1328">
+      <c r="A1328" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1328" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1328" t="n">
+        <v>0.485000014305115</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>0.495000004768372</v>
+      </c>
+      <c r="E1328" t="n">
+        <v>0.48199999332428</v>
+      </c>
+      <c r="F1328" t="n">
+        <v>0.495000004768372</v>
+      </c>
+      <c r="G1328" t="n">
+        <v>0.495000004768372</v>
+      </c>
+      <c r="H1328" t="n">
+        <v>100500</v>
+      </c>
+      <c r="I1328" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -38890,6 +38890,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1329">
+      <c r="A1329" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1329" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1329" t="n">
+        <v>0.485000014305115</v>
+      </c>
+      <c r="D1329" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="E1329" t="n">
+        <v>0.474999994039536</v>
+      </c>
+      <c r="F1329" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="G1329" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="H1329" t="n">
+        <v>25500</v>
+      </c>
+      <c r="I1329" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -38919,6 +38919,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1330">
+      <c r="A1330" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1330" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1330" t="n">
+        <v>0.483000010251999</v>
+      </c>
+      <c r="D1330" t="n">
+        <v>0.486999988555908</v>
+      </c>
+      <c r="E1330" t="n">
+        <v>0.476000010967255</v>
+      </c>
+      <c r="F1330" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="G1330" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="H1330" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I1330" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -38948,6 +38948,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1331">
+      <c r="A1331" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1331" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1331" t="n">
+        <v>0.485000014305115</v>
+      </c>
+      <c r="D1331" t="n">
+        <v>0.486999988555908</v>
+      </c>
+      <c r="E1331" t="n">
+        <v>0.485000014305115</v>
+      </c>
+      <c r="F1331" t="n">
+        <v>0.486999988555908</v>
+      </c>
+      <c r="G1331" t="n">
+        <v>0.486999988555908</v>
+      </c>
+      <c r="H1331" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1331" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -38977,6 +38977,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1332">
+      <c r="A1332" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1332" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1332" t="n">
+        <v>0.488999992609024</v>
+      </c>
+      <c r="D1332" t="n">
+        <v>0.495000004768372</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>0.472000002861023</v>
+      </c>
+      <c r="F1332" t="n">
+        <v>0.479000002145767</v>
+      </c>
+      <c r="G1332" t="n">
+        <v>0.479000002145767</v>
+      </c>
+      <c r="H1332" t="n">
+        <v>52500</v>
+      </c>
+      <c r="I1332" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -39006,6 +39006,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1333">
+      <c r="A1333" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1333" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1333" t="n">
+        <v>0.479000002145767</v>
+      </c>
+      <c r="D1333" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="E1333" t="n">
+        <v>0.465000003576279</v>
+      </c>
+      <c r="F1333" t="n">
+        <v>0.465000003576279</v>
+      </c>
+      <c r="G1333" t="n">
+        <v>0.465000003576279</v>
+      </c>
+      <c r="H1333" t="n">
+        <v>39000</v>
+      </c>
+      <c r="I1333" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NUS.MI.xlsx
+++ b/data/NUS.MI.xlsx
@@ -39035,6 +39035,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1334">
+      <c r="A1334" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1334" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1334" t="n">
+        <v>0.462999999523163</v>
+      </c>
+      <c r="D1334" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="E1334" t="n">
+        <v>0.441000014543533</v>
+      </c>
+      <c r="F1334" t="n">
+        <v>0.444999992847443</v>
+      </c>
+      <c r="G1334" t="n">
+        <v>0.444999992847443</v>
+      </c>
+      <c r="H1334" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I1334" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
